--- a/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>design pattern</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -528,172 +528,172 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.9231</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>design pattern</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>architectural pattern</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7692</v>
+        <v>0.6667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8696</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architectural pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6667</v>
+        <v>0.2222</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6667</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -701,45 +701,53 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.6667</v>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>component</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.3636</v>
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4706</v>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>design pattern</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -528,63 +528,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>design pattern</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9231</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8571</v>
+        <v>0.8125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.8966</v>
       </c>
     </row>
     <row r="6">
@@ -621,90 +621,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.2727</v>
       </c>
       <c r="H7" t="n">
         <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6667</v>
+        <v>0.3529</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
       <c r="G8" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.2667</v>
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -725,21 +725,19 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
@@ -528,91 +528,91 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>design pattern</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9231</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.9231</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>architectural pattern</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8966</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architectural pattern</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="I6" t="n">
         <v>0.6667</v>
@@ -621,87 +621,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>design pattern</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2727</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3529</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.6667</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +723,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_by_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,11 +457,6 @@
           <t>recall</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,86 +485,77 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>component</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9231</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9231</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.9231</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architectural pattern</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -577,146 +563,131 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>connector (unit-pairs)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7143</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6667</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>design pattern</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6667</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>architectural pattern</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>design pattern</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -726,24 +697,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
